--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="66">
   <si>
     <t/>
   </si>
@@ -22,12 +22,6 @@
     <t>OK</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>nor ahmed</t>
-  </si>
-  <si>
     <t>Invalid</t>
   </si>
   <si>
@@ -61,75 +55,81 @@
     <t>انصراف</t>
   </si>
   <si>
-    <t>01/06/2026 08:25 ص</t>
-  </si>
-  <si>
-    <t>01/06/2026 05:39 م</t>
+    <t>04/06/2026 05:37 م</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Ahmed</t>
+  </si>
+  <si>
+    <t>01/06/2026 09:50 ص</t>
+  </si>
+  <si>
+    <t>01/06/2026 05:55 م</t>
+  </si>
+  <si>
+    <t>03/06/2026 08:54 ص</t>
+  </si>
+  <si>
+    <t>03/06/2026 05:32 م</t>
+  </si>
+  <si>
+    <t>04/06/2026 09:50 ص</t>
+  </si>
+  <si>
+    <t>06/06/2026 01:15 م</t>
+  </si>
+  <si>
+    <t>06/06/2026 05:32 م</t>
+  </si>
+  <si>
+    <t>07/06/2026 10:33 ص</t>
+  </si>
+  <si>
+    <t>07/06/2026 05:33 م</t>
+  </si>
+  <si>
+    <t>08/06/2026 10:54 ص</t>
+  </si>
+  <si>
+    <t>08/06/2026 04:52 م</t>
+  </si>
+  <si>
+    <t>09/06/2026 09:11 ص</t>
+  </si>
+  <si>
+    <t>10/06/2026 09:50 ص</t>
+  </si>
+  <si>
+    <t>11/06/2026 11:06 ص</t>
+  </si>
+  <si>
+    <t>11/06/2026 05:32 م</t>
+  </si>
+  <si>
+    <t>14/06/2026 09:20 ص</t>
+  </si>
+  <si>
+    <t>14/06/2026 05:30 م</t>
+  </si>
+  <si>
+    <t>14/06/2026 08:20 ص</t>
+  </si>
+  <si>
+    <t>14/06/2026 11:20 ص</t>
+  </si>
+  <si>
+    <t>10/06/2026 01:10 م</t>
+  </si>
+  <si>
+    <t>09/06/2026 04:39 م</t>
   </si>
   <si>
     <t>02/06/2026 08:27 ص</t>
   </si>
   <si>
-    <t>02/06/2026 05:30 م</t>
-  </si>
-  <si>
-    <t>03/06/2026 08:28 ص</t>
-  </si>
-  <si>
-    <t>03/06/2026 05:40 م</t>
-  </si>
-  <si>
-    <t>04/06/2026 08:26 ص</t>
-  </si>
-  <si>
-    <t>04/06/2026 05:37 م</t>
-  </si>
-  <si>
-    <t>06/06/2026 08:31 ص</t>
-  </si>
-  <si>
-    <t>06/06/2026 05:42 م</t>
-  </si>
-  <si>
-    <t>07/06/2026 08:25 ص</t>
-  </si>
-  <si>
-    <t>07/06/2026 05:34 م</t>
-  </si>
-  <si>
-    <t>08/06/2026 08:36 ص</t>
-  </si>
-  <si>
-    <t>08/06/2026 05:59 م</t>
-  </si>
-  <si>
-    <t>09/06/2026 08:22 ص</t>
-  </si>
-  <si>
-    <t>09/06/2026 07:00 م</t>
-  </si>
-  <si>
-    <t>10/06/2026 08:28 ص</t>
-  </si>
-  <si>
-    <t>10/06/2026 05:46 م</t>
-  </si>
-  <si>
-    <t>11/06/2026 08:28 ص</t>
-  </si>
-  <si>
-    <t>11/06/2026 05:37 م</t>
-  </si>
-  <si>
-    <t>13/06/2026 08:24 ص</t>
-  </si>
-  <si>
-    <t>13/06/2026 05:41 م</t>
-  </si>
-  <si>
-    <t>14/06/2026 08:25 ص</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -166,163 +166,52 @@
     <t>09/06/2026 08:30 ص</t>
   </si>
   <si>
-    <t>09/06/2026 06:59 م</t>
-  </si>
-  <si>
-    <t>Repeat</t>
-  </si>
-  <si>
-    <t>10/06/2026 05:33 م</t>
-  </si>
-  <si>
-    <t>11/06/2026 08:22 ص</t>
-  </si>
-  <si>
-    <t>11/06/2026 05:38 م</t>
-  </si>
-  <si>
-    <t>13/06/2026 08:27 ص</t>
-  </si>
-  <si>
-    <t>13/06/2026 05:35 م</t>
-  </si>
-  <si>
-    <t>14/06/2026 08:23 ص</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Basant</t>
-  </si>
-  <si>
-    <t>01/06/2026 08:27 ص</t>
-  </si>
-  <si>
-    <t>01/06/2026 05:34 م</t>
-  </si>
-  <si>
-    <t>02/06/2026 08:22 ص</t>
-  </si>
-  <si>
-    <t>02/06/2026 05:35 م</t>
-  </si>
-  <si>
-    <t>03/06/2026 08:24 ص</t>
-  </si>
-  <si>
-    <t>03/06/2026 05:33 م</t>
-  </si>
-  <si>
-    <t>04/06/2026 08:24 ص</t>
-  </si>
-  <si>
-    <t>06/06/2026 05:30 م</t>
-  </si>
-  <si>
-    <t>07/06/2026 05:30 م</t>
-  </si>
-  <si>
-    <t>08/06/2026 08:24 ص</t>
-  </si>
-  <si>
-    <t>08/06/2026 05:36 م</t>
-  </si>
-  <si>
-    <t>08/06/2026 05:37 م</t>
-  </si>
-  <si>
-    <t>09/06/2026 08:26 ص</t>
-  </si>
-  <si>
-    <t>09/06/2026 07:04 م</t>
-  </si>
-  <si>
-    <t>10/06/2026 08:27 ص</t>
-  </si>
-  <si>
-    <t>10/06/2026 05:40 م</t>
-  </si>
-  <si>
-    <t>11/06/2026 08:30 ص</t>
-  </si>
-  <si>
-    <t>11/06/2026 05:31 م</t>
-  </si>
-  <si>
-    <t>13/06/2026 08:23 ص</t>
-  </si>
-  <si>
-    <t>13/06/2026 05:33 م</t>
-  </si>
-  <si>
-    <t>14/06/2026 08:29 ص</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>Ahmed</t>
-  </si>
-  <si>
-    <t>01/06/2026 09:50 ص</t>
-  </si>
-  <si>
-    <t>01/06/2026 05:55 م</t>
-  </si>
-  <si>
-    <t>03/06/2026 08:54 ص</t>
-  </si>
-  <si>
-    <t>03/06/2026 05:32 م</t>
-  </si>
-  <si>
-    <t>04/06/2026 09:50 ص</t>
-  </si>
-  <si>
-    <t>06/06/2026 01:15 م</t>
-  </si>
-  <si>
-    <t>06/06/2026 05:32 م</t>
-  </si>
-  <si>
-    <t>07/06/2026 10:33 ص</t>
-  </si>
-  <si>
-    <t>07/06/2026 05:33 م</t>
-  </si>
-  <si>
-    <t>08/06/2026 10:54 ص</t>
-  </si>
-  <si>
-    <t>08/06/2026 04:52 م</t>
-  </si>
-  <si>
-    <t>09/06/2026 09:11 ص</t>
-  </si>
-  <si>
-    <t>09/06/2026 05:39 م</t>
-  </si>
-  <si>
-    <t>10/06/2026 09:50 ص</t>
-  </si>
-  <si>
-    <t>11/06/2026 11:06 ص</t>
-  </si>
-  <si>
-    <t>11/06/2026 05:32 م</t>
-  </si>
-  <si>
-    <t>14/06/2026 09:20 ص</t>
-  </si>
-  <si>
-    <t>14/06/2026 05:30 م</t>
-  </si>
-  <si>
-    <t>14/06/2026 08:20 ص</t>
-  </si>
-  <si>
-    <t>14/06/2026 11:20 ص</t>
+    <t>15/06/2026 09:50 ص</t>
+  </si>
+  <si>
+    <t>15/06/2026 05:55 م</t>
+  </si>
+  <si>
+    <t>16/06/2026 08:54 ص</t>
+  </si>
+  <si>
+    <t>16/06/2026 05:32 م</t>
+  </si>
+  <si>
+    <t>17/06/2026 09:50 ص</t>
+  </si>
+  <si>
+    <t>17/06/2026 05:37 م</t>
+  </si>
+  <si>
+    <t>18/06/2026 01:15 م</t>
+  </si>
+  <si>
+    <t>18/06/2026 05:32 م</t>
+  </si>
+  <si>
+    <t>19/06/2026 10:33 ص</t>
+  </si>
+  <si>
+    <t>19/06/2026 05:33 م</t>
+  </si>
+  <si>
+    <t>20/06/2026 10:54 ص</t>
+  </si>
+  <si>
+    <t>20/06/2026 04:52 م</t>
+  </si>
+  <si>
+    <t>21/06/2026 09:11 ص</t>
+  </si>
+  <si>
+    <t>21/06/2026 04:39 م</t>
+  </si>
+  <si>
+    <t>22/06/2026 09:50 ص</t>
+  </si>
+  <si>
+    <t>22/06/2026 01:10 م</t>
   </si>
 </sst>
 </file>
@@ -670,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H375"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -679,45 +568,45 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
@@ -731,25 +620,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>0</v>
@@ -757,19 +646,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>0</v>
@@ -783,25 +672,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>0</v>
@@ -809,19 +698,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>0</v>
@@ -835,25 +724,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>0</v>
@@ -861,25 +750,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>0</v>
@@ -887,19 +776,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>0</v>
@@ -913,19 +802,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>0</v>
@@ -939,25 +828,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>0</v>
@@ -965,19 +854,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>0</v>
@@ -991,25 +880,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>0</v>
@@ -1017,19 +906,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>0</v>
@@ -1043,25 +932,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>0</v>
@@ -1069,19 +958,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>0</v>
@@ -1095,25 +984,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>0</v>
@@ -1121,19 +1010,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>0</v>
@@ -1147,25 +1036,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>0</v>
@@ -1173,19 +1062,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>0</v>
@@ -1199,19 +1088,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>0</v>
@@ -1225,19 +1114,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -1251,25 +1140,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>0</v>
@@ -1277,19 +1166,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
@@ -1303,19 +1192,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>0</v>
@@ -1329,19 +1218,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>40</v>
+        <v>15</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>0</v>
@@ -1355,19 +1244,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>0</v>
@@ -1381,25 +1270,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>42</v>
+        <v>15</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>0</v>
@@ -1407,19 +1296,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>43</v>
+        <v>15</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>0</v>
@@ -1433,25 +1322,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>0</v>
@@ -1459,19 +1348,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>0</v>
@@ -1485,25 +1374,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>0</v>
@@ -1511,19 +1400,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>47</v>
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>0</v>
@@ -1537,19 +1426,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>0</v>
@@ -1563,22 +1452,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>49</v>
+        <v>15</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>1</v>
@@ -1589,25 +1478,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>0</v>
@@ -1615,25 +1504,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>0</v>
@@ -1641,19 +1530,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>0</v>
@@ -1667,25 +1556,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>0</v>
@@ -1702,10 +1591,10 @@
         <v>39</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>0</v>
@@ -1728,10 +1617,10 @@
         <v>39</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>0</v>
@@ -1754,10 +1643,10 @@
         <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>0</v>
@@ -1780,16 +1669,16 @@
         <v>39</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>0</v>
@@ -1806,10 +1695,10 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>0</v>
@@ -1823,19 +1712,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>0</v>
@@ -1849,25 +1738,25 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>0</v>
@@ -1875,25 +1764,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>0</v>
@@ -1901,25 +1790,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>0</v>
@@ -1927,19 +1816,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>0</v>
@@ -1953,1069 +1842,429 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
@@ -4923,7 +4172,7 @@
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
-      <c r="F281" s="1"/>
+      <c r="F281" s="3"/>
       <c r="G281" s="1"/>
       <c r="H281" s="1"/>
     </row>
@@ -4933,7 +4182,7 @@
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
-      <c r="F282" s="1"/>
+      <c r="F282" s="3"/>
       <c r="G282" s="1"/>
       <c r="H282" s="1"/>
     </row>
@@ -4973,7 +4222,7 @@
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
-      <c r="F286" s="1"/>
+      <c r="F286" s="3"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
     </row>
@@ -5127,746 +4376,6 @@
       <c r="G301" s="1"/>
       <c r="H301" s="1"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" s="1"/>
-      <c r="B302" s="1"/>
-      <c r="C302" s="1"/>
-      <c r="D302" s="1"/>
-      <c r="E302" s="1"/>
-      <c r="F302" s="1"/>
-      <c r="G302" s="1"/>
-      <c r="H302" s="1"/>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" s="1"/>
-      <c r="B303" s="1"/>
-      <c r="C303" s="1"/>
-      <c r="D303" s="1"/>
-      <c r="E303" s="1"/>
-      <c r="F303" s="1"/>
-      <c r="G303" s="1"/>
-      <c r="H303" s="1"/>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A304" s="1"/>
-      <c r="B304" s="1"/>
-      <c r="C304" s="1"/>
-      <c r="D304" s="1"/>
-      <c r="E304" s="1"/>
-      <c r="F304" s="1"/>
-      <c r="G304" s="1"/>
-      <c r="H304" s="1"/>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A305" s="1"/>
-      <c r="B305" s="1"/>
-      <c r="C305" s="1"/>
-      <c r="D305" s="1"/>
-      <c r="E305" s="1"/>
-      <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
-      <c r="H305" s="1"/>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A306" s="1"/>
-      <c r="B306" s="1"/>
-      <c r="C306" s="1"/>
-      <c r="D306" s="1"/>
-      <c r="E306" s="1"/>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
-      <c r="H306" s="1"/>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A307" s="1"/>
-      <c r="B307" s="1"/>
-      <c r="C307" s="1"/>
-      <c r="D307" s="1"/>
-      <c r="E307" s="1"/>
-      <c r="F307" s="1"/>
-      <c r="G307" s="1"/>
-      <c r="H307" s="1"/>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A308" s="1"/>
-      <c r="B308" s="1"/>
-      <c r="C308" s="1"/>
-      <c r="D308" s="1"/>
-      <c r="E308" s="1"/>
-      <c r="F308" s="1"/>
-      <c r="G308" s="1"/>
-      <c r="H308" s="1"/>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A309" s="1"/>
-      <c r="B309" s="1"/>
-      <c r="C309" s="1"/>
-      <c r="D309" s="1"/>
-      <c r="E309" s="1"/>
-      <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
-      <c r="H309" s="1"/>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A310" s="1"/>
-      <c r="B310" s="1"/>
-      <c r="C310" s="1"/>
-      <c r="D310" s="1"/>
-      <c r="E310" s="1"/>
-      <c r="F310" s="1"/>
-      <c r="G310" s="1"/>
-      <c r="H310" s="1"/>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A311" s="1"/>
-      <c r="B311" s="1"/>
-      <c r="C311" s="1"/>
-      <c r="D311" s="1"/>
-      <c r="E311" s="1"/>
-      <c r="F311" s="1"/>
-      <c r="G311" s="1"/>
-      <c r="H311" s="1"/>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A312" s="1"/>
-      <c r="B312" s="1"/>
-      <c r="C312" s="1"/>
-      <c r="D312" s="1"/>
-      <c r="E312" s="1"/>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
-      <c r="H312" s="1"/>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A313" s="1"/>
-      <c r="B313" s="1"/>
-      <c r="C313" s="1"/>
-      <c r="D313" s="1"/>
-      <c r="E313" s="1"/>
-      <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
-      <c r="H313" s="1"/>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314" s="1"/>
-      <c r="B314" s="1"/>
-      <c r="C314" s="1"/>
-      <c r="D314" s="1"/>
-      <c r="E314" s="1"/>
-      <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
-      <c r="H314" s="1"/>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A315" s="1"/>
-      <c r="B315" s="1"/>
-      <c r="C315" s="1"/>
-      <c r="D315" s="1"/>
-      <c r="E315" s="1"/>
-      <c r="F315" s="1"/>
-      <c r="G315" s="1"/>
-      <c r="H315" s="1"/>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316" s="1"/>
-      <c r="B316" s="1"/>
-      <c r="C316" s="1"/>
-      <c r="D316" s="1"/>
-      <c r="E316" s="1"/>
-      <c r="F316" s="1"/>
-      <c r="G316" s="1"/>
-      <c r="H316" s="1"/>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A317" s="1"/>
-      <c r="B317" s="1"/>
-      <c r="C317" s="1"/>
-      <c r="D317" s="1"/>
-      <c r="E317" s="1"/>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
-      <c r="H317" s="1"/>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A318" s="1"/>
-      <c r="B318" s="1"/>
-      <c r="C318" s="1"/>
-      <c r="D318" s="1"/>
-      <c r="E318" s="1"/>
-      <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
-      <c r="H318" s="1"/>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A319" s="1"/>
-      <c r="B319" s="1"/>
-      <c r="C319" s="1"/>
-      <c r="D319" s="1"/>
-      <c r="E319" s="1"/>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
-      <c r="H319" s="1"/>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A320" s="1"/>
-      <c r="B320" s="1"/>
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
-      <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
-      <c r="H320" s="1"/>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321" s="1"/>
-      <c r="B321" s="1"/>
-      <c r="C321" s="1"/>
-      <c r="D321" s="1"/>
-      <c r="E321" s="1"/>
-      <c r="F321" s="1"/>
-      <c r="G321" s="1"/>
-      <c r="H321" s="1"/>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A322" s="1"/>
-      <c r="B322" s="1"/>
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
-      <c r="E322" s="1"/>
-      <c r="F322" s="1"/>
-      <c r="G322" s="1"/>
-      <c r="H322" s="1"/>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323" s="1"/>
-      <c r="B323" s="1"/>
-      <c r="C323" s="1"/>
-      <c r="D323" s="1"/>
-      <c r="E323" s="1"/>
-      <c r="F323" s="1"/>
-      <c r="G323" s="1"/>
-      <c r="H323" s="1"/>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A324" s="1"/>
-      <c r="B324" s="1"/>
-      <c r="C324" s="1"/>
-      <c r="D324" s="1"/>
-      <c r="E324" s="1"/>
-      <c r="F324" s="1"/>
-      <c r="G324" s="1"/>
-      <c r="H324" s="1"/>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A325" s="1"/>
-      <c r="B325" s="1"/>
-      <c r="C325" s="1"/>
-      <c r="D325" s="1"/>
-      <c r="E325" s="1"/>
-      <c r="F325" s="1"/>
-      <c r="G325" s="1"/>
-      <c r="H325" s="1"/>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A326" s="1"/>
-      <c r="B326" s="1"/>
-      <c r="C326" s="1"/>
-      <c r="D326" s="1"/>
-      <c r="E326" s="1"/>
-      <c r="F326" s="1"/>
-      <c r="G326" s="1"/>
-      <c r="H326" s="1"/>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A327" s="1"/>
-      <c r="B327" s="1"/>
-      <c r="C327" s="1"/>
-      <c r="D327" s="1"/>
-      <c r="E327" s="1"/>
-      <c r="F327" s="1"/>
-      <c r="G327" s="1"/>
-      <c r="H327" s="1"/>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A328" s="1"/>
-      <c r="B328" s="1"/>
-      <c r="C328" s="1"/>
-      <c r="D328" s="1"/>
-      <c r="E328" s="1"/>
-      <c r="F328" s="1"/>
-      <c r="G328" s="1"/>
-      <c r="H328" s="1"/>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
-      <c r="C329" s="1"/>
-      <c r="D329" s="1"/>
-      <c r="E329" s="1"/>
-      <c r="F329" s="1"/>
-      <c r="G329" s="1"/>
-      <c r="H329" s="1"/>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A330" s="1"/>
-      <c r="B330" s="1"/>
-      <c r="C330" s="1"/>
-      <c r="D330" s="1"/>
-      <c r="E330" s="1"/>
-      <c r="F330" s="1"/>
-      <c r="G330" s="1"/>
-      <c r="H330" s="1"/>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A331" s="1"/>
-      <c r="B331" s="1"/>
-      <c r="C331" s="1"/>
-      <c r="D331" s="1"/>
-      <c r="E331" s="1"/>
-      <c r="F331" s="1"/>
-      <c r="G331" s="1"/>
-      <c r="H331" s="1"/>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A332" s="1"/>
-      <c r="B332" s="1"/>
-      <c r="C332" s="1"/>
-      <c r="D332" s="1"/>
-      <c r="E332" s="1"/>
-      <c r="F332" s="1"/>
-      <c r="G332" s="1"/>
-      <c r="H332" s="1"/>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A333" s="1"/>
-      <c r="B333" s="1"/>
-      <c r="C333" s="1"/>
-      <c r="D333" s="1"/>
-      <c r="E333" s="1"/>
-      <c r="F333" s="1"/>
-      <c r="G333" s="1"/>
-      <c r="H333" s="1"/>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A334" s="1"/>
-      <c r="B334" s="1"/>
-      <c r="C334" s="1"/>
-      <c r="D334" s="1"/>
-      <c r="E334" s="1"/>
-      <c r="F334" s="1"/>
-      <c r="G334" s="1"/>
-      <c r="H334" s="1"/>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A335" s="1"/>
-      <c r="B335" s="1"/>
-      <c r="C335" s="1"/>
-      <c r="D335" s="1"/>
-      <c r="E335" s="1"/>
-      <c r="F335" s="1"/>
-      <c r="G335" s="1"/>
-      <c r="H335" s="1"/>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A336" s="1"/>
-      <c r="B336" s="1"/>
-      <c r="C336" s="1"/>
-      <c r="D336" s="1"/>
-      <c r="E336" s="1"/>
-      <c r="F336" s="1"/>
-      <c r="G336" s="1"/>
-      <c r="H336" s="1"/>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A337" s="1"/>
-      <c r="B337" s="1"/>
-      <c r="C337" s="1"/>
-      <c r="D337" s="1"/>
-      <c r="E337" s="1"/>
-      <c r="F337" s="1"/>
-      <c r="G337" s="1"/>
-      <c r="H337" s="1"/>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A338" s="1"/>
-      <c r="B338" s="1"/>
-      <c r="C338" s="1"/>
-      <c r="D338" s="1"/>
-      <c r="E338" s="1"/>
-      <c r="F338" s="1"/>
-      <c r="G338" s="1"/>
-      <c r="H338" s="1"/>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A339" s="1"/>
-      <c r="B339" s="1"/>
-      <c r="C339" s="1"/>
-      <c r="D339" s="1"/>
-      <c r="E339" s="1"/>
-      <c r="F339" s="1"/>
-      <c r="G339" s="1"/>
-      <c r="H339" s="1"/>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A340" s="1"/>
-      <c r="B340" s="1"/>
-      <c r="C340" s="1"/>
-      <c r="D340" s="1"/>
-      <c r="E340" s="1"/>
-      <c r="F340" s="1"/>
-      <c r="G340" s="1"/>
-      <c r="H340" s="1"/>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A341" s="1"/>
-      <c r="B341" s="1"/>
-      <c r="C341" s="1"/>
-      <c r="D341" s="1"/>
-      <c r="E341" s="1"/>
-      <c r="F341" s="1"/>
-      <c r="G341" s="1"/>
-      <c r="H341" s="1"/>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A342" s="1"/>
-      <c r="B342" s="1"/>
-      <c r="C342" s="1"/>
-      <c r="D342" s="1"/>
-      <c r="E342" s="1"/>
-      <c r="F342" s="1"/>
-      <c r="G342" s="1"/>
-      <c r="H342" s="1"/>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A343" s="1"/>
-      <c r="B343" s="1"/>
-      <c r="C343" s="1"/>
-      <c r="D343" s="1"/>
-      <c r="E343" s="1"/>
-      <c r="F343" s="1"/>
-      <c r="G343" s="1"/>
-      <c r="H343" s="1"/>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A344" s="1"/>
-      <c r="B344" s="1"/>
-      <c r="C344" s="1"/>
-      <c r="D344" s="1"/>
-      <c r="E344" s="1"/>
-      <c r="F344" s="1"/>
-      <c r="G344" s="1"/>
-      <c r="H344" s="1"/>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A345" s="1"/>
-      <c r="B345" s="1"/>
-      <c r="C345" s="1"/>
-      <c r="D345" s="1"/>
-      <c r="E345" s="1"/>
-      <c r="F345" s="1"/>
-      <c r="G345" s="1"/>
-      <c r="H345" s="1"/>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A346" s="1"/>
-      <c r="B346" s="1"/>
-      <c r="C346" s="1"/>
-      <c r="D346" s="1"/>
-      <c r="E346" s="1"/>
-      <c r="F346" s="1"/>
-      <c r="G346" s="1"/>
-      <c r="H346" s="1"/>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A347" s="1"/>
-      <c r="B347" s="1"/>
-      <c r="C347" s="1"/>
-      <c r="D347" s="1"/>
-      <c r="E347" s="1"/>
-      <c r="F347" s="1"/>
-      <c r="G347" s="1"/>
-      <c r="H347" s="1"/>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A348" s="1"/>
-      <c r="B348" s="1"/>
-      <c r="C348" s="1"/>
-      <c r="D348" s="1"/>
-      <c r="E348" s="1"/>
-      <c r="F348" s="1"/>
-      <c r="G348" s="1"/>
-      <c r="H348" s="1"/>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A349" s="1"/>
-      <c r="B349" s="1"/>
-      <c r="C349" s="1"/>
-      <c r="D349" s="1"/>
-      <c r="E349" s="1"/>
-      <c r="F349" s="1"/>
-      <c r="G349" s="1"/>
-      <c r="H349" s="1"/>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A350" s="1"/>
-      <c r="B350" s="1"/>
-      <c r="C350" s="1"/>
-      <c r="D350" s="1"/>
-      <c r="E350" s="1"/>
-      <c r="F350" s="1"/>
-      <c r="G350" s="1"/>
-      <c r="H350" s="1"/>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A351" s="1"/>
-      <c r="B351" s="1"/>
-      <c r="C351" s="1"/>
-      <c r="D351" s="1"/>
-      <c r="E351" s="1"/>
-      <c r="F351" s="1"/>
-      <c r="G351" s="1"/>
-      <c r="H351" s="1"/>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A352" s="1"/>
-      <c r="B352" s="1"/>
-      <c r="C352" s="1"/>
-      <c r="D352" s="1"/>
-      <c r="E352" s="1"/>
-      <c r="F352" s="1"/>
-      <c r="G352" s="1"/>
-      <c r="H352" s="1"/>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A353" s="1"/>
-      <c r="B353" s="1"/>
-      <c r="C353" s="1"/>
-      <c r="D353" s="1"/>
-      <c r="E353" s="1"/>
-      <c r="F353" s="1"/>
-      <c r="G353" s="1"/>
-      <c r="H353" s="1"/>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A354" s="1"/>
-      <c r="B354" s="1"/>
-      <c r="C354" s="1"/>
-      <c r="D354" s="1"/>
-      <c r="E354" s="1"/>
-      <c r="F354" s="1"/>
-      <c r="G354" s="1"/>
-      <c r="H354" s="1"/>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A355" s="1"/>
-      <c r="B355" s="1"/>
-      <c r="C355" s="1"/>
-      <c r="D355" s="1"/>
-      <c r="E355" s="1"/>
-      <c r="F355" s="3"/>
-      <c r="G355" s="1"/>
-      <c r="H355" s="1"/>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A356" s="1"/>
-      <c r="B356" s="1"/>
-      <c r="C356" s="1"/>
-      <c r="D356" s="1"/>
-      <c r="E356" s="1"/>
-      <c r="F356" s="3"/>
-      <c r="G356" s="1"/>
-      <c r="H356" s="1"/>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A357" s="1"/>
-      <c r="B357" s="1"/>
-      <c r="C357" s="1"/>
-      <c r="D357" s="1"/>
-      <c r="E357" s="1"/>
-      <c r="F357" s="1"/>
-      <c r="G357" s="1"/>
-      <c r="H357" s="1"/>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A358" s="1"/>
-      <c r="B358" s="1"/>
-      <c r="C358" s="1"/>
-      <c r="D358" s="1"/>
-      <c r="E358" s="1"/>
-      <c r="F358" s="1"/>
-      <c r="G358" s="1"/>
-      <c r="H358" s="1"/>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A359" s="1"/>
-      <c r="B359" s="1"/>
-      <c r="C359" s="1"/>
-      <c r="D359" s="1"/>
-      <c r="E359" s="1"/>
-      <c r="F359" s="1"/>
-      <c r="G359" s="1"/>
-      <c r="H359" s="1"/>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A360" s="1"/>
-      <c r="B360" s="1"/>
-      <c r="C360" s="1"/>
-      <c r="D360" s="1"/>
-      <c r="E360" s="1"/>
-      <c r="F360" s="3"/>
-      <c r="G360" s="1"/>
-      <c r="H360" s="1"/>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A361" s="1"/>
-      <c r="B361" s="1"/>
-      <c r="C361" s="1"/>
-      <c r="D361" s="1"/>
-      <c r="E361" s="1"/>
-      <c r="F361" s="1"/>
-      <c r="G361" s="1"/>
-      <c r="H361" s="1"/>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A362" s="1"/>
-      <c r="B362" s="1"/>
-      <c r="C362" s="1"/>
-      <c r="D362" s="1"/>
-      <c r="E362" s="1"/>
-      <c r="F362" s="1"/>
-      <c r="G362" s="1"/>
-      <c r="H362" s="1"/>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A363" s="1"/>
-      <c r="B363" s="1"/>
-      <c r="C363" s="1"/>
-      <c r="D363" s="1"/>
-      <c r="E363" s="1"/>
-      <c r="F363" s="1"/>
-      <c r="G363" s="1"/>
-      <c r="H363" s="1"/>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A364" s="1"/>
-      <c r="B364" s="1"/>
-      <c r="C364" s="1"/>
-      <c r="D364" s="1"/>
-      <c r="E364" s="1"/>
-      <c r="F364" s="1"/>
-      <c r="G364" s="1"/>
-      <c r="H364" s="1"/>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A365" s="1"/>
-      <c r="B365" s="1"/>
-      <c r="C365" s="1"/>
-      <c r="D365" s="1"/>
-      <c r="E365" s="1"/>
-      <c r="F365" s="1"/>
-      <c r="G365" s="1"/>
-      <c r="H365" s="1"/>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A366" s="1"/>
-      <c r="B366" s="1"/>
-      <c r="C366" s="1"/>
-      <c r="D366" s="1"/>
-      <c r="E366" s="1"/>
-      <c r="F366" s="1"/>
-      <c r="G366" s="1"/>
-      <c r="H366" s="1"/>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A367" s="1"/>
-      <c r="B367" s="1"/>
-      <c r="C367" s="1"/>
-      <c r="D367" s="1"/>
-      <c r="E367" s="1"/>
-      <c r="F367" s="1"/>
-      <c r="G367" s="1"/>
-      <c r="H367" s="1"/>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A368" s="1"/>
-      <c r="B368" s="1"/>
-      <c r="C368" s="1"/>
-      <c r="D368" s="1"/>
-      <c r="E368" s="1"/>
-      <c r="F368" s="1"/>
-      <c r="G368" s="1"/>
-      <c r="H368" s="1"/>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A369" s="1"/>
-      <c r="B369" s="1"/>
-      <c r="C369" s="1"/>
-      <c r="D369" s="1"/>
-      <c r="E369" s="1"/>
-      <c r="F369" s="1"/>
-      <c r="G369" s="1"/>
-      <c r="H369" s="1"/>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A370" s="1"/>
-      <c r="B370" s="1"/>
-      <c r="C370" s="1"/>
-      <c r="D370" s="1"/>
-      <c r="E370" s="1"/>
-      <c r="F370" s="1"/>
-      <c r="G370" s="1"/>
-      <c r="H370" s="1"/>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
-      <c r="C371" s="1"/>
-      <c r="D371" s="1"/>
-      <c r="E371" s="1"/>
-      <c r="F371" s="1"/>
-      <c r="G371" s="1"/>
-      <c r="H371" s="1"/>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
-      <c r="C372" s="1"/>
-      <c r="D372" s="1"/>
-      <c r="E372" s="1"/>
-      <c r="F372" s="1"/>
-      <c r="G372" s="1"/>
-      <c r="H372" s="1"/>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A373" s="1"/>
-      <c r="B373" s="1"/>
-      <c r="C373" s="1"/>
-      <c r="D373" s="1"/>
-      <c r="E373" s="1"/>
-      <c r="F373" s="1"/>
-      <c r="G373" s="1"/>
-      <c r="H373" s="1"/>
-    </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A374" s="1"/>
-      <c r="B374" s="1"/>
-      <c r="C374" s="1"/>
-      <c r="D374" s="1"/>
-      <c r="E374" s="1"/>
-      <c r="F374" s="1"/>
-      <c r="G374" s="1"/>
-      <c r="H374" s="1"/>
-    </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A375" s="1"/>
-      <c r="B375" s="1"/>
-      <c r="C375" s="1"/>
-      <c r="D375" s="1"/>
-      <c r="E375" s="1"/>
-      <c r="F375" s="1"/>
-      <c r="G375" s="1"/>
-      <c r="H375" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="67">
   <si>
     <t/>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>22/06/2026 01:10 م</t>
+  </si>
+  <si>
+    <t>nor ahmed</t>
   </si>
 </sst>
 </file>
@@ -1867,114 +1870,290 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
+      <c r="A51" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="A52" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="A53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="A54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
+      <c r="A55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
+      <c r="A56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
+      <c r="A57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
+      <c r="A58" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
+      <c r="A59" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+      <c r="A60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
+      <c r="A61" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="67">
   <si>
     <t/>
   </si>
@@ -562,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1922,238 +1922,94 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
@@ -4261,7 +4117,7 @@
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
-      <c r="F272" s="1"/>
+      <c r="F272" s="3"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1"/>
     </row>
@@ -4271,7 +4127,7 @@
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
-      <c r="F273" s="1"/>
+      <c r="F273" s="3"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1"/>
     </row>
@@ -4311,7 +4167,7 @@
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
+      <c r="F277" s="3"/>
       <c r="G277" s="1"/>
       <c r="H277" s="1"/>
     </row>
@@ -4351,7 +4207,7 @@
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
-      <c r="F281" s="3"/>
+      <c r="F281" s="1"/>
       <c r="G281" s="1"/>
       <c r="H281" s="1"/>
     </row>
@@ -4361,7 +4217,7 @@
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
-      <c r="F282" s="3"/>
+      <c r="F282" s="1"/>
       <c r="G282" s="1"/>
       <c r="H282" s="1"/>
     </row>
@@ -4401,7 +4257,7 @@
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
-      <c r="F286" s="3"/>
+      <c r="F286" s="1"/>
       <c r="G286" s="1"/>
       <c r="H286" s="1"/>
     </row>
@@ -4465,96 +4321,6 @@
       <c r="G292" s="1"/>
       <c r="H292" s="1"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A293" s="1"/>
-      <c r="B293" s="1"/>
-      <c r="C293" s="1"/>
-      <c r="D293" s="1"/>
-      <c r="E293" s="1"/>
-      <c r="F293" s="1"/>
-      <c r="G293" s="1"/>
-      <c r="H293" s="1"/>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A294" s="1"/>
-      <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
-      <c r="D294" s="1"/>
-      <c r="E294" s="1"/>
-      <c r="F294" s="1"/>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A295" s="1"/>
-      <c r="B295" s="1"/>
-      <c r="C295" s="1"/>
-      <c r="D295" s="1"/>
-      <c r="E295" s="1"/>
-      <c r="F295" s="1"/>
-      <c r="G295" s="1"/>
-      <c r="H295" s="1"/>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A296" s="1"/>
-      <c r="B296" s="1"/>
-      <c r="C296" s="1"/>
-      <c r="D296" s="1"/>
-      <c r="E296" s="1"/>
-      <c r="F296" s="1"/>
-      <c r="G296" s="1"/>
-      <c r="H296" s="1"/>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A297" s="1"/>
-      <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
-      <c r="D297" s="1"/>
-      <c r="E297" s="1"/>
-      <c r="F297" s="1"/>
-      <c r="G297" s="1"/>
-      <c r="H297" s="1"/>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A298" s="1"/>
-      <c r="B298" s="1"/>
-      <c r="C298" s="1"/>
-      <c r="D298" s="1"/>
-      <c r="E298" s="1"/>
-      <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
-      <c r="H298" s="1"/>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A299" s="1"/>
-      <c r="B299" s="1"/>
-      <c r="C299" s="1"/>
-      <c r="D299" s="1"/>
-      <c r="E299" s="1"/>
-      <c r="F299" s="1"/>
-      <c r="G299" s="1"/>
-      <c r="H299" s="1"/>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300" s="1"/>
-      <c r="B300" s="1"/>
-      <c r="C300" s="1"/>
-      <c r="D300" s="1"/>
-      <c r="E300" s="1"/>
-      <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
-      <c r="H300" s="1"/>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A301" s="1"/>
-      <c r="B301" s="1"/>
-      <c r="C301" s="1"/>
-      <c r="D301" s="1"/>
-      <c r="E301" s="1"/>
-      <c r="F301" s="1"/>
-      <c r="G301" s="1"/>
-      <c r="H301" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>

--- a/test.xlsx
+++ b/test.xlsx
@@ -133,9 +133,6 @@
     <t>23</t>
   </si>
   <si>
-    <t>Shahd</t>
-  </si>
-  <si>
     <t>02/06/2026 05:41 م</t>
   </si>
   <si>
@@ -214,7 +211,10 @@
     <t>22/06/2026 01:10 م</t>
   </si>
   <si>
-    <t>nor ahmed</t>
+    <t>bassant</t>
+  </si>
+  <si>
+    <t>lobna</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1178,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>12</v>
@@ -1230,7 +1230,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>11</v>
@@ -1256,7 +1256,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>12</v>
@@ -1282,7 +1282,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>11</v>
@@ -1308,7 +1308,7 @@
         <v>15</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>12</v>
@@ -1334,7 +1334,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>11</v>
@@ -1360,7 +1360,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>12</v>
@@ -1386,7 +1386,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>11</v>
@@ -1412,7 +1412,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
@@ -1438,7 +1438,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>11</v>
@@ -1464,7 +1464,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>11</v>
@@ -1490,7 +1490,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>11</v>
@@ -1516,7 +1516,7 @@
         <v>15</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>12</v>
@@ -1542,7 +1542,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>11</v>
@@ -1568,7 +1568,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>11</v>
@@ -1590,8 +1590,8 @@
       <c r="B40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>39</v>
+      <c r="C40" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>37</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>12</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>11</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>12</v>
@@ -1695,10 +1695,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>11</v>
@@ -1721,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>12</v>
@@ -1747,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>11</v>
@@ -1773,10 +1773,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>12</v>
@@ -1799,10 +1799,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>11</v>
@@ -1825,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>12</v>
@@ -1851,10 +1851,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>11</v>
@@ -1906,7 +1906,7 @@
         <v>66</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>12</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="69">
   <si>
     <t/>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>lobna</t>
+  </si>
+  <si>
+    <t>dina</t>
+  </si>
+  <si>
+    <t>fatma</t>
   </si>
 </sst>
 </file>
@@ -1922,44 +1928,108 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="A53" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="A54" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
+      <c r="A55" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
+      <c r="A56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
